--- a/docs/MACROPAGE-Quiz-API-Endpoints.xlsx
+++ b/docs/MACROPAGE-Quiz-API-Endpoints.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="105">
   <si>
     <t>Group</t>
   </si>
@@ -87,40 +87,22 @@
     <t>{ title: string, autoSeedQuestions?: boolean (default true) }</t>
   </si>
   <si>
-    <t>QuizSession document (includes _id, status: "draft", currentQuestionIndex: -1, questionIds: [])</t>
-  </si>
-  <si>
-    <t>Creates a session; auto-seeds the 5 default questions unless autoSeedQuestions is false.</t>
-  </si>
-  <si>
-    <t>/api/sessions/:id/open-registration</t>
+    <t>QuizSession document (_id, status: "draft", questionIds: [])</t>
+  </si>
+  <si>
+    <t>Creates a session; auto-seeds the 5 default questions unless autoSeedQuestions is false. Registration is open immediately — no separate open-registration step.</t>
+  </si>
+  <si>
+    <t>/api/sessions/:id/start</t>
   </si>
   <si>
     <t>(none)</t>
   </si>
   <si>
-    <t>Updated QuizSession (status: "registration_open")</t>
-  </si>
-  <si>
-    <t>Only valid from status "draft". Broadcasts session:state over socket.</t>
-  </si>
-  <si>
-    <t>/api/sessions/:id/start</t>
-  </si>
-  <si>
-    <t>Updated QuizSession (status: "in_progress", currentQuestionIndex: 0)</t>
-  </si>
-  <si>
-    <t>Only valid from "registration_open" and requires questions configured. Broadcasts session:state + question:new.</t>
-  </si>
-  <si>
-    <t>/api/sessions/:id/next-question</t>
-  </si>
-  <si>
-    <t>Updated QuizSession (currentQuestionIndex incremented)</t>
-  </si>
-  <si>
-    <t>Errors if already on the final question (call /end instead). Broadcasts session:state + question:new.</t>
+    <t>Updated QuizSession (status: "in_progress")</t>
+  </si>
+  <si>
+    <t>Only valid from status "draft" and requires questions configured. Broadcasts session:state + questions:all (ALL 5 questions at once — no per-question pacing).</t>
   </si>
   <si>
     <t>/api/sessions/:id/end</t>
@@ -129,7 +111,7 @@
     <t>Updated QuizSession (status: "ended")</t>
   </si>
   <si>
-    <t>Broadcasts session:state + quiz:ended + a final leaderboard:update.</t>
+    <t>Only valid from "in_progress". Broadcasts session:state + quiz:ended + a final leaderboard:update. There is no "next question" admin control — the whole state machine is draft -&gt; in_progress -&gt; ended.</t>
   </si>
   <si>
     <t>/api/sessions/:id/leaderboard</t>
@@ -165,22 +147,22 @@
     <t>/api/sessions/:id/state?participantId=&lt;id&gt;</t>
   </si>
   <si>
-    <t>{ sessionId, title, status, currentQuestionIndex, totalQuestions, hasAnsweredCurrentQuestion: boolean|null }</t>
-  </si>
-  <si>
-    <t>participantId query param is optional; when provided, tells the client if it already answered the current question (for showing "waiting" state after refresh).</t>
+    <t>{ sessionId, title, status, totalQuestions, answeredQuestionIds: string[]|null }</t>
+  </si>
+  <si>
+    <t>participantId query param is optional; when provided (and status is not "draft"), returns which question IDs this participant has already answered — use this to resume mid-quiz after a reload.</t>
   </si>
   <si>
     <t>Questions (Public)</t>
   </si>
   <si>
-    <t>/api/questions/:sessionId/current</t>
-  </si>
-  <si>
-    <t>{ id, text, order, timeLimitSeconds, dimension, options: [{key, text}], index, totalQuestions }</t>
-  </si>
-  <si>
-    <t>No correct-answer/points info is exposed. 404 if no active question.</t>
+    <t>/api/questions/:sessionId</t>
+  </si>
+  <si>
+    <t>SanitizedQuestion[]: [{ id, text, order, timeLimitSeconds, dimension, options: [{key, text}] }]</t>
+  </si>
+  <si>
+    <t>Returns ALL questions at once (not one "current" question) — the quiz is self-paced, not admin-paced. 400 if session is still "draft" (quiz not started, questions must not leak early). No correct-answer/points info is exposed.</t>
   </si>
   <si>
     <t>Participants (Public)</t>
@@ -198,7 +180,7 @@
     <t>{ participantId: string, sessionToken: string }</t>
   </si>
   <si>
-    <t>Only works when session.status === "registration_open". Store sessionToken client-side (localStorage) — it is the bearer token for all subsequent participant calls.</t>
+    <t>Works any time the session is not yet "ended" — participants can land on the session URL directly and register whenever, no separate registration-open gate. Store sessionToken client-side (localStorage) — it is the bearer token for all subsequent participant calls.</t>
   </si>
   <si>
     <t>PATCH</t>
@@ -237,10 +219,10 @@
     <t>{ questionId: string (Mongo ObjectId), selectedKey: "A"|"B"|"C"|"D", timeTakenMs: number (&gt;= 0) }</t>
   </si>
   <si>
-    <t>Created Answer record (points are computed server-side, not trusted from client)</t>
-  </si>
-  <si>
-    <t>One answer per (participant, question) enforced by a unique index — resubmits should be treated as an error by the UI.</t>
+    <t>{ success: true } (points are computed server-side, not trusted from client)</t>
+  </si>
+  <si>
+    <t>Self-paced: any question belonging to the session can be answered in any order, as long as session.status === "in_progress". One answer per (participant, question) enforced by a unique index — resubmits return 409 Conflict.</t>
   </si>
   <si>
     <t>Analysis (Public)</t>
@@ -252,7 +234,7 @@
     <t>AnalysisReport: { participantId, sessionId, generatedAt, techScore, archetype, dimensionScores: {growthMindset, customerRelationship, strategicThinking, investmentDiscipline, digitalReadiness}, reportJson: {headline, businessSnapshot, mindsetProfile, goalRoadmap[], techRecommendation} }</t>
   </si>
   <si>
-    <t>"Analyze My Business" button. Triggers AI generation on first call; cached (idempotent) on repeat calls. Can take a few seconds — show a loading/"AI thinking" state.</t>
+    <t>"Analyze My Business" section on the results screen (shown right after quiz:ended, alongside the leaderboard). Triggers AI generation on first call; cached (idempotent) on repeat calls. Can take a few seconds — show a loading/"AI thinking" state.</t>
   </si>
   <si>
     <t>Existing AnalysisReport, or 404/null if not generated yet</t>
@@ -279,7 +261,7 @@
     <t>{ sessionId: string, participantId?: string, role: "participant" | "display" | "admin" }</t>
   </si>
   <si>
-    <t>Send immediately after connecting to the "quiz" namespace. Joins the session room (and a display sub-room if role is "display"). Server replies with session:state (and question:new if quiz is in progress).</t>
+    <t>Send immediately after connecting to the "quiz" namespace. Joins the session room (and a display sub-room if role is "display"). Server replies with session:state (and questions:all if the quiz is in_progress or already ended).</t>
   </si>
   <si>
     <t>Server → Client</t>
@@ -288,19 +270,19 @@
     <t>session:state</t>
   </si>
   <si>
-    <t>{ sessionId, title, status, currentQuestionIndex, totalQuestions, hasAnsweredCurrentQuestion }</t>
-  </si>
-  <si>
-    <t>Sent on join and on every admin state transition. Drives which screen the client shows (waiting room / question / leaderboard / final rank).</t>
-  </si>
-  <si>
-    <t>question:new</t>
-  </si>
-  <si>
-    <t>{ question: {id, text, order, timeLimitSeconds, dimension, options}, index, totalQuestions, timeLimitSeconds, serverTimestamp }</t>
-  </si>
-  <si>
-    <t>Fired when the admin starts the quiz or advances to the next question. Use serverTimestamp to sync the countdown timer across devices.</t>
+    <t>{ sessionId, title, status, totalQuestions, answeredQuestionIds }</t>
+  </si>
+  <si>
+    <t>Sent on join and on every admin state transition (start/end). Drives which screen the client shows (waiting room / quiz / results). status is one of draft | in_progress | ended — that's the whole state machine.</t>
+  </si>
+  <si>
+    <t>questions:all</t>
+  </si>
+  <si>
+    <t>{ questions: SanitizedQuestion[], totalQuestions, serverTimestamp }</t>
+  </si>
+  <si>
+    <t>Fired ONCE when the admin starts the quiz (replaces the old per-question "question:new" push — there is no next-question admin control). Contains all 5 questions; the client paces the participant through them itself and submits each via POST /api/answers as answered.</t>
   </si>
   <si>
     <t>leaderboard:update</t>
@@ -309,7 +291,7 @@
     <t>{ top: [{participantId, name, businessName?, score, rank}], totalAnswered }</t>
   </si>
   <si>
-    <t>Debounced ~1s after answers come in. top is limited to top 10 — use for the live projector display, not full rankings.</t>
+    <t>Debounced ~1s after answers come in. top is limited to top 10 — use for the live projector display, not full rankings. totalAnswered is a good proxy for "quiz progress" since there is no per-question index anymore.</t>
   </si>
   <si>
     <t>quiz:ended</t>
@@ -318,13 +300,22 @@
     <t>{}</t>
   </si>
   <si>
-    <t>Signals participants to move to their final-rank screen; followed by a final leaderboard:update.</t>
+    <t>Signals participants to go straight to the results screen (rank + leaderboard + "Analyze My Business"); followed by a final leaderboard:update.</t>
   </si>
   <si>
     <t>Base URL: all REST routes are prefixed with /api except /health.</t>
   </si>
   <si>
     <t>Socket.IO namespace: /quiz (e.g. io("https://&lt;host&gt;/quiz")).</t>
+  </si>
+  <si>
+    <t>State machine: draft -&gt; in_progress -&gt; ended. Only two admin actions: POST /api/sessions/:id/start and POST /api/sessions/:id/end. There is no "open registration" step and no "next question" step.</t>
+  </si>
+  <si>
+    <t>Registration: participants can register any time the session is not "ended" — there is no gating status to check first.</t>
+  </si>
+  <si>
+    <t>Questions: all 5 are sent to the client at once (GET /api/questions/:sessionId or the questions:all socket event) when the quiz starts. Pacing through them is entirely client-side; the server does not track or push a "current question".</t>
   </si>
   <si>
     <t>Participant auth: sessionToken returned from POST /api/participants/register, sent as "Authorization: Bearer &lt;sessionToken&gt;".</t>
@@ -731,13 +722,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="7" width="55" customWidth="1"/>
+    <col min="5" max="6" width="55" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -883,7 +875,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>33</v>
@@ -892,7 +884,7 @@
         <v>22</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>34</v>
@@ -906,7 +898,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>36</v>
@@ -915,7 +907,7 @@
         <v>22</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>37</v>
@@ -949,232 +941,186 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1191,18 +1137,19 @@
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="4" width="65" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -1210,72 +1157,72 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1287,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" style="4" customWidth="1"/>
@@ -1300,32 +1247,47 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MACROPAGE-Quiz-API-Endpoints.xlsx
+++ b/docs/MACROPAGE-Quiz-API-Endpoints.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="108">
   <si>
     <t>Group</t>
   </si>
@@ -93,6 +93,12 @@
     <t>Creates a session; auto-seeds the 5 default questions unless autoSeedQuestions is false. Registration is open immediately — no separate open-registration step.</t>
   </si>
   <si>
+    <t>QuizSession[] — every session ever created, newest first (sorted by createdAt desc)</t>
+  </si>
+  <si>
+    <t>Quiz history / session picker. Sessions are never deleted, so past events (and their leaderboard/participants/export) stay browsable via this list + the existing per-session routes below.</t>
+  </si>
+  <si>
     <t>/api/sessions/:id/start</t>
   </si>
   <si>
@@ -120,7 +126,7 @@
     <t>LeaderboardEntry[]: { participantId, name, businessName?, score, rank }[]</t>
   </si>
   <si>
-    <t>Full ranked list (not just top N) — for admin dashboard, not the projector display.</t>
+    <t>Full ranked list (not just top N) — for admin dashboard, not the projector display. Works for past (ended) sessions too.</t>
   </si>
   <si>
     <t>/api/sessions/:id/participants</t>
@@ -129,7 +135,7 @@
     <t>Participant[] (full documents incl. onboarding fields)</t>
   </si>
   <si>
-    <t>For admin review / manual export.</t>
+    <t>For admin review / manual export. Works for past (ended) sessions too.</t>
   </si>
   <si>
     <t>/api/sessions/:id/export.csv</t>
@@ -138,7 +144,7 @@
     <t>text/csv file download (Content-Disposition: attachment)</t>
   </si>
   <si>
-    <t>Columns: Name, WhatsApp Number, Business Name, Business Category, Goal, Goal (Other), Score, Rank, Registered At.</t>
+    <t>Columns: Name, WhatsApp Number, Business Name, Business Category, Goal, Goal (Other), Score, Rank, Registered At. Works for past (ended) sessions too.</t>
   </si>
   <si>
     <t>Sessions (Public)</t>
@@ -234,7 +240,7 @@
     <t>AnalysisReport: { participantId, sessionId, generatedAt, techScore, archetype, dimensionScores: {growthMindset, customerRelationship, strategicThinking, investmentDiscipline, digitalReadiness}, reportJson: {headline, businessSnapshot, mindsetProfile, goalRoadmap[], techRecommendation} }</t>
   </si>
   <si>
-    <t>"Analyze My Business" section on the results screen (shown right after quiz:ended, alongside the leaderboard). Triggers AI generation on first call; cached (idempotent) on repeat calls. Can take a few seconds — show a loading/"AI thinking" state.</t>
+    <t>"Analyze My Business" section on the results screen (shown right after quiz:ended, alongside the leaderboard). Triggers AI generation on first call; cached (idempotent) on repeat calls. Can take a few seconds — show a loading/"AI thinking" state. Returns 503 with a clear message if the AI call fails after retrying once (e.g. bad/missing ANTHROPIC_API_KEY).</t>
   </si>
   <si>
     <t>Existing AnalysisReport, or 404/null if not generated yet</t>
@@ -310,6 +316,9 @@
   </si>
   <si>
     <t>State machine: draft -&gt; in_progress -&gt; ended. Only two admin actions: POST /api/sessions/:id/start and POST /api/sessions/:id/end. There is no "open registration" step and no "next question" step.</t>
+  </si>
+  <si>
+    <t>Session history: sessions are never deleted. GET /api/sessions lists all of them (newest first) so past events stay browsable via the existing per-session leaderboard/participants/export routes.</t>
   </si>
   <si>
     <t>Registration: participants can register any time the session is not "ended" — there is no gating status to check first.</t>
@@ -722,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -829,22 +838,22 @@
         <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -855,19 +864,19 @@
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -875,22 +884,22 @@
         <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -901,7 +910,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>22</v>
@@ -910,10 +919,10 @@
         <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -924,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>22</v>
@@ -933,44 +942,44 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>10</v>
@@ -979,148 +988,171 @@
         <v>11</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1143,13 +1175,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -1157,72 +1189,72 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1234,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" style="4" customWidth="1"/>
@@ -1247,47 +1279,52 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MACROPAGE-Quiz-API-Endpoints.xlsx
+++ b/docs/MACROPAGE-Quiz-API-Endpoints.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="116">
   <si>
     <t>Group</t>
   </si>
@@ -75,22 +75,46 @@
     <t>Use accessToken as "Authorization: Bearer &lt;token&gt;" on all admin routes below.</t>
   </si>
   <si>
+    <t>Questions (Admin)</t>
+  </si>
+  <si>
+    <t>/api/questions/trivia/seed</t>
+  </si>
+  <si>
+    <t>Admin JWT</t>
+  </si>
+  <si>
+    <t>(none)</t>
+  </si>
+  <si>
+    <t>SanitizedQuestion[] — the full 50-question trivia bank</t>
+  </si>
+  <si>
+    <t>Idempotent: if any type="trivia" questions already exist in the DB, returns them unchanged instead of inserting duplicates. Safe to call more than once (e.g. on every deploy).</t>
+  </si>
+  <si>
+    <t>/api/questions/trivia/bank</t>
+  </si>
+  <si>
+    <t>(SanitizedQuestion &amp; { correctKey: "A"|"B"|"C"|"D"|null })[]</t>
+  </si>
+  <si>
+    <t>Admin-only listing used to hand-pick trivia questions for a session. Includes correctKey (unlike every participant-facing question route, which never exposes the answer).</t>
+  </si>
+  <si>
     <t>Sessions (Admin)</t>
   </si>
   <si>
     <t>/api/sessions</t>
   </si>
   <si>
-    <t>Admin JWT</t>
-  </si>
-  <si>
-    <t>{ title: string, autoSeedQuestions?: boolean (default true) }</t>
+    <t>{ title: string, autoSeedQuestions?: boolean (default true), triviaQuestionIds?: string[], triviaCount?: number (1-50) }</t>
   </si>
   <si>
     <t>QuizSession document (_id, status: "draft", questionIds: [])</t>
   </si>
   <si>
-    <t>Creates a session; auto-seeds the 5 default questions unless autoSeedQuestions is false. Registration is open immediately — no separate open-registration step.</t>
+    <t>Creates a session; auto-seeds the 5 default mindset questions unless autoSeedQuestions is false. Optionally appends trivia: triviaQuestionIds is an explicit, ordered pick (takes priority if both are sent); triviaCount randomly samples that many from the trivia bank via $sample. Registration is open immediately — no separate open-registration step.</t>
   </si>
   <si>
     <t>QuizSession[] — every session ever created, newest first (sorted by createdAt desc)</t>
@@ -102,9 +126,6 @@
     <t>/api/sessions/:id/start</t>
   </si>
   <si>
-    <t>(none)</t>
-  </si>
-  <si>
     <t>Updated QuizSession (status: "in_progress")</t>
   </si>
   <si>
@@ -165,10 +186,10 @@
     <t>/api/questions/:sessionId</t>
   </si>
   <si>
-    <t>SanitizedQuestion[]: [{ id, text, order, timeLimitSeconds, dimension, options: [{key, text}] }]</t>
-  </si>
-  <si>
-    <t>Returns ALL questions at once (not one "current" question) — the quiz is self-paced, not admin-paced. 400 if session is still "draft" (quiz not started, questions must not leak early). No correct-answer/points info is exposed.</t>
+    <t>SanitizedQuestion[]: [{ id, text, order, timeLimitSeconds, type: "mindset"|"trivia", dimension?, options: [{key, text}] }]</t>
+  </si>
+  <si>
+    <t>Returns EVERY question configured for the session at once (mindset + trivia mixed, in the order the admin set), not one "current" question — the quiz is self-paced, not admin-paced. 400 if session is still "draft" (quiz not started, questions must not leak early). No correct-answer/points info is exposed (that only appears in the admin-only trivia bank listing).</t>
   </si>
   <si>
     <t>Participants (Public)</t>
@@ -240,7 +261,7 @@
     <t>AnalysisReport: { participantId, sessionId, generatedAt, techScore, archetype, dimensionScores: {growthMindset, customerRelationship, strategicThinking, investmentDiscipline, digitalReadiness}, reportJson: {headline, businessSnapshot, mindsetProfile, goalRoadmap[], techRecommendation} }</t>
   </si>
   <si>
-    <t>"Analyze My Business" section on the results screen (shown right after quiz:ended, alongside the leaderboard). Triggers AI generation on first call; cached (idempotent) on repeat calls. Can take a few seconds — show a loading/"AI thinking" state. Returns 503 with a clear message if the AI call fails after retrying once (e.g. bad/missing ANTHROPIC_API_KEY).</t>
+    <t>"Analyze My Business" section on the results screen (shown right after quiz:ended, alongside the leaderboard). Only mindset answers feed dimensionScores/archetype/techScore — trivia answers are excluded from this calculation entirely (they still count toward the leaderboard score). Triggers AI generation on first call; cached (idempotent) on repeat calls. Can take a few seconds — show a loading/"AI thinking" state. Returns 503 with a clear message if the AI call fails after retrying once (e.g. bad/missing ANTHROPIC_API_KEY).</t>
   </si>
   <si>
     <t>Existing AnalysisReport, or 404/null if not generated yet</t>
@@ -337,6 +358,9 @@
   </si>
   <si>
     <t>CORS origin and JWT secret are environment-configured; see .env.example in the repo.</t>
+  </si>
+  <si>
+    <t>Trivia bank: a reusable pool of 50 general-knowledge questions (type="trivia"), separate from the 5 fixed mindset questions (type="mindset"). Seed once with POST /api/questions/trivia/seed (idempotent), then pick 8-12 per event via triviaQuestionIds or triviaCount on POST /api/sessions. Trivia scores count toward the leaderboard but are excluded from the "Analyze My Business" dimension/archetype calculation.</t>
   </si>
 </sst>
 </file>
@@ -731,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -841,7 +865,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>22</v>
@@ -850,113 +874,113 @@
         <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>22</v>
@@ -965,15 +989,15 @@
         <v>11</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>8</v>
@@ -982,7 +1006,7 @@
         <v>45</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
@@ -996,163 +1020,209 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>77</v>
+      <c r="F20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1175,13 +1245,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -1189,72 +1259,72 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" style="4" customWidth="1"/>
@@ -1279,52 +1349,57 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>107</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MACROPAGE-Quiz-API-Endpoints.xlsx
+++ b/docs/MACROPAGE-Quiz-API-Endpoints.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="121">
   <si>
     <t>Group</t>
   </si>
@@ -78,15 +78,33 @@
     <t>Questions (Admin)</t>
   </si>
   <si>
+    <t>/api/questions/mindset/seed</t>
+  </si>
+  <si>
+    <t>Admin JWT</t>
+  </si>
+  <si>
+    <t>(none)</t>
+  </si>
+  <si>
+    <t>SanitizedQuestion[] — the 15-question mindset bank (3 variants per dimension)</t>
+  </si>
+  <si>
+    <t>Idempotent: if any type="mindset" questions already exist, returns them unchanged. Must be seeded before a session can start.</t>
+  </si>
+  <si>
+    <t>/api/questions/mindset/bank</t>
+  </si>
+  <si>
+    <t>SanitizedQuestion[] — full mindset bank</t>
+  </si>
+  <si>
+    <t>For admin review only — this bank is never picked from at session-creation time; every participant gets their own random assignment instead (see GET /api/questions/:sessionId).</t>
+  </si>
+  <si>
     <t>/api/questions/trivia/seed</t>
   </si>
   <si>
-    <t>Admin JWT</t>
-  </si>
-  <si>
-    <t>(none)</t>
-  </si>
-  <si>
     <t>SanitizedQuestion[] — the full 50-question trivia bank</t>
   </si>
   <si>
@@ -102,19 +120,34 @@
     <t>Admin-only listing used to hand-pick trivia questions for a session. Includes correctKey (unlike every participant-facing question route, which never exposes the answer).</t>
   </si>
   <si>
+    <t>Questions (Public)</t>
+  </si>
+  <si>
+    <t>/api/questions/:sessionId</t>
+  </si>
+  <si>
+    <t>Session Token (Bearer)</t>
+  </si>
+  <si>
+    <t>SanitizedQuestion[]: [{ id, text, order, timeLimitSeconds, type: "mindset"|"trivia", dimension?, options: [{key, text}] }]</t>
+  </si>
+  <si>
+    <t>THIS PARTICIPANT'S OWN question set, not a shared session list: 5 mindset questions (one randomly sampled per dimension from the bank, assigned on first call and persisted on Participant.assignedQuestionIds — same set returned on every later call/reload) + the session's shared trivia questions appended after. 400 if session is still "draft". No correct-answer/points info exposed.</t>
+  </si>
+  <si>
     <t>Sessions (Admin)</t>
   </si>
   <si>
     <t>/api/sessions</t>
   </si>
   <si>
-    <t>{ title: string, autoSeedQuestions?: boolean (default true), triviaQuestionIds?: string[], triviaCount?: number (1-50) }</t>
-  </si>
-  <si>
-    <t>QuizSession document (_id, status: "draft", questionIds: [])</t>
-  </si>
-  <si>
-    <t>Creates a session; auto-seeds the 5 default mindset questions unless autoSeedQuestions is false. Optionally appends trivia: triviaQuestionIds is an explicit, ordered pick (takes priority if both are sent); triviaCount randomly samples that many from the trivia bank via $sample. Registration is open immediately — no separate open-registration step.</t>
+    <t>{ title: string, triviaQuestionIds?: string[], triviaCount?: number (1-50) }</t>
+  </si>
+  <si>
+    <t>QuizSession document (_id, status: "draft", questionIds: [] — trivia only)</t>
+  </si>
+  <si>
+    <t>Creates a session. Mindset questions are NOT configured here — they are assigned per participant, not per session. Optionally appends trivia: triviaQuestionIds is an explicit, ordered pick (takes priority if both are sent); triviaCount randomly samples that many from the trivia bank via $sample. Registration is open immediately — no separate open-registration step.</t>
   </si>
   <si>
     <t>QuizSession[] — every session ever created, newest first (sorted by createdAt desc)</t>
@@ -129,7 +162,7 @@
     <t>Updated QuizSession (status: "in_progress")</t>
   </si>
   <si>
-    <t>Only valid from status "draft" and requires questions configured. Broadcasts session:state + questions:all (ALL 5 questions at once — no per-question pacing).</t>
+    <t>Only valid from status "draft". 400s if the global mindset bank is empty (call POST /api/questions/mindset/seed first) — this replaced the old "session has no questions configured" check, since mindset is no longer session-scoped.</t>
   </si>
   <si>
     <t>/api/sessions/:id/end</t>
@@ -153,7 +186,7 @@
     <t>/api/sessions/:id/participants</t>
   </si>
   <si>
-    <t>Participant[] (full documents incl. onboarding fields)</t>
+    <t>Participant[] (full documents incl. onboarding fields and assignedQuestionIds)</t>
   </si>
   <si>
     <t>For admin review / manual export. Works for past (ended) sessions too.</t>
@@ -177,19 +210,7 @@
     <t>{ sessionId, title, status, totalQuestions, answeredQuestionIds: string[]|null }</t>
   </si>
   <si>
-    <t>participantId query param is optional; when provided (and status is not "draft"), returns which question IDs this participant has already answered — use this to resume mid-quiz after a reload.</t>
-  </si>
-  <si>
-    <t>Questions (Public)</t>
-  </si>
-  <si>
-    <t>/api/questions/:sessionId</t>
-  </si>
-  <si>
-    <t>SanitizedQuestion[]: [{ id, text, order, timeLimitSeconds, type: "mindset"|"trivia", dimension?, options: [{key, text}] }]</t>
-  </si>
-  <si>
-    <t>Returns EVERY question configured for the session at once (mindset + trivia mixed, in the order the admin set), not one "current" question — the quiz is self-paced, not admin-paced. 400 if session is still "draft" (quiz not started, questions must not leak early). No correct-answer/points info is exposed (that only appears in the admin-only trivia bank listing).</t>
+    <t>participantId query param is optional; when provided (and status is not "draft"), returns which question IDs this participant has already answered — use this to resume mid-quiz after a reload. totalQuestions = 5 (mindset, fixed) + session.questionIds.length (trivia).</t>
   </si>
   <si>
     <t>Participants (Public)</t>
@@ -216,9 +237,6 @@
     <t>/api/participants/:id/onboarding</t>
   </si>
   <si>
-    <t>Session Token (Bearer)</t>
-  </si>
-  <si>
     <t>{ businessName?: string, businessCategory?: string, goal: "grow_customers"|"grow_revenue"|"other", goalOther?: string (required if goal === "other") }</t>
   </si>
   <si>
@@ -249,7 +267,7 @@
     <t>{ success: true } (points are computed server-side, not trusted from client)</t>
   </si>
   <si>
-    <t>Self-paced: any question belonging to the session can be answered in any order, as long as session.status === "in_progress". One answer per (participant, question) enforced by a unique index — resubmits return 409 Conflict.</t>
+    <t>Self-paced: any question belonging to the participant's own assigned mindset set OR the session's trivia list can be answered in any order, as long as session.status === "in_progress". One answer per (participant, question) enforced by a unique index — resubmits return 409 Conflict.</t>
   </si>
   <si>
     <t>Analysis (Public)</t>
@@ -261,7 +279,7 @@
     <t>AnalysisReport: { participantId, sessionId, generatedAt, techScore, archetype, dimensionScores: {growthMindset, customerRelationship, strategicThinking, investmentDiscipline, digitalReadiness}, reportJson: {headline, businessSnapshot, mindsetProfile, goalRoadmap[], techRecommendation} }</t>
   </si>
   <si>
-    <t>"Analyze My Business" section on the results screen (shown right after quiz:ended, alongside the leaderboard). Only mindset answers feed dimensionScores/archetype/techScore — trivia answers are excluded from this calculation entirely (they still count toward the leaderboard score). Triggers AI generation on first call; cached (idempotent) on repeat calls. Can take a few seconds — show a loading/"AI thinking" state. Returns 503 with a clear message if the AI call fails after retrying once (e.g. bad/missing ANTHROPIC_API_KEY).</t>
+    <t>"Analyze My Business" section on the results screen (shown right after quiz:ended, alongside the leaderboard). Built only from this participant's 5 personally-assigned mindset answers — trivia answers are excluded entirely (they still count toward the leaderboard score). Triggers AI generation on first call; cached (idempotent) on repeat calls. Can take a few seconds — show a loading/"AI thinking" state. Returns 503 with a clear message if the AI call fails after retrying once (e.g. bad/missing ANTHROPIC_API_KEY).</t>
   </si>
   <si>
     <t>Existing AnalysisReport, or 404/null if not generated yet</t>
@@ -288,7 +306,7 @@
     <t>{ sessionId: string, participantId?: string, role: "participant" | "display" | "admin" }</t>
   </si>
   <si>
-    <t>Send immediately after connecting to the "quiz" namespace. Joins the session room (and a display sub-room if role is "display"). Server replies with session:state (and questions:all if the quiz is in_progress or already ended).</t>
+    <t>Send immediately after connecting to the "quiz" namespace. Joins the session room (and a display sub-room if role is "display"). Server replies with session:state only — there is no question-content push (see notes below).</t>
   </si>
   <si>
     <t>Server → Client</t>
@@ -300,16 +318,7 @@
     <t>{ sessionId, title, status, totalQuestions, answeredQuestionIds }</t>
   </si>
   <si>
-    <t>Sent on join and on every admin state transition (start/end). Drives which screen the client shows (waiting room / quiz / results). status is one of draft | in_progress | ended — that's the whole state machine.</t>
-  </si>
-  <si>
-    <t>questions:all</t>
-  </si>
-  <si>
-    <t>{ questions: SanitizedQuestion[], totalQuestions, serverTimestamp }</t>
-  </si>
-  <si>
-    <t>Fired ONCE when the admin starts the quiz (replaces the old per-question "question:new" push — there is no next-question admin control). Contains all 5 questions; the client paces the participant through them itself and submits each via POST /api/answers as answered.</t>
+    <t>Sent on join and on every admin state transition (start/end). Drives which screen the client shows (waiting room / quiz / results). status is one of draft | in_progress | ended. When status becomes in_progress, that is the client's cue to call GET /api/questions/:sessionId to fetch its OWN personalized question set — there is no socket broadcast of question content, since each participant's set differs.</t>
   </si>
   <si>
     <t>leaderboard:update</t>
@@ -318,7 +327,7 @@
     <t>{ top: [{participantId, name, businessName?, score, rank}], totalAnswered }</t>
   </si>
   <si>
-    <t>Debounced ~1s after answers come in. top is limited to top 10 — use for the live projector display, not full rankings. totalAnswered is a good proxy for "quiz progress" since there is no per-question index anymore.</t>
+    <t>Debounced ~1s after answers come in. top is limited to top 10 — use for the live projector display, not full rankings. totalAnswered is a good proxy for "quiz progress" since there is no shared per-question index anymore.</t>
   </si>
   <si>
     <t>quiz:ended</t>
@@ -339,13 +348,19 @@
     <t>State machine: draft -&gt; in_progress -&gt; ended. Only two admin actions: POST /api/sessions/:id/start and POST /api/sessions/:id/end. There is no "open registration" step and no "next question" step.</t>
   </si>
   <si>
+    <t>PERSONALIZED QUESTIONS: each participant gets their own random pick of 1 mindset question per dimension (5 total, from a 15-question bank with 3 variants per dimension), assigned on their first GET /api/questions/:sessionId call and persisted on Participant.assignedQuestionIds — the same set is returned on every later call. Different participants very likely see different specific wording for the same dimension. This guarantees full dimension coverage per participant, so the AI analysis always has complete data.</t>
+  </si>
+  <si>
+    <t>Two independent question banks, both admin-seeded once and idempotent: mindset (POST /api/questions/mindset/seed, 15 questions) and trivia (POST /api/questions/trivia/seed, 50 questions). Only the trivia bank is picked from at session-creation time (triviaQuestionIds / triviaCount) — mindset is never session-scoped.</t>
+  </si>
+  <si>
     <t>Session history: sessions are never deleted. GET /api/sessions lists all of them (newest first) so past events stay browsable via the existing per-session leaderboard/participants/export routes.</t>
   </si>
   <si>
     <t>Registration: participants can register any time the session is not "ended" — there is no gating status to check first.</t>
   </si>
   <si>
-    <t>Questions: all 5 are sent to the client at once (GET /api/questions/:sessionId or the questions:all socket event) when the quiz starts. Pacing through them is entirely client-side; the server does not track or push a "current question".</t>
+    <t>No socket event carries question content. Once session:state.status becomes in_progress, the client must call GET /api/questions/:sessionId (bearer sessionToken) to fetch its own set — this was previously a broadcast "questions:all" socket event, removed because content is now personalized per participant and cannot be broadcast identically to a room.</t>
   </si>
   <si>
     <t>Participant auth: sessionToken returned from POST /api/participants/register, sent as "Authorization: Bearer &lt;sessionToken&gt;".</t>
@@ -357,10 +372,10 @@
     <t>Answers and onboarding are write-once/guarded server-side — do not rely on client-side checks alone.</t>
   </si>
   <si>
+    <t>AI analysis (POST /api/participants/:id/analysis) is computed ONLY from the participant's 5 mindset answers. Trivia answers count toward the leaderboard score but are fully excluded from dimensionScores/archetype/techScore.</t>
+  </si>
+  <si>
     <t>CORS origin and JWT secret are environment-configured; see .env.example in the repo.</t>
-  </si>
-  <si>
-    <t>Trivia bank: a reusable pool of 50 general-knowledge questions (type="trivia"), separate from the 5 fixed mindset questions (type="mindset"). Seed once with POST /api/questions/trivia/seed (idempotent), then pick 8-12 per event via triviaQuestionIds or triviaCount on POST /api/sessions. Trivia scores count toward the leaderboard but are excluded from the "Analyze My Business" dimension/archetype calculation.</t>
   </si>
 </sst>
 </file>
@@ -755,14 +770,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="6" width="55" customWidth="1"/>
-    <col min="7" max="7" width="60" customWidth="1"/>
+    <col min="7" max="7" width="65" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -882,36 +897,36 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>22</v>
@@ -920,67 +935,67 @@
         <v>11</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>22</v>
@@ -989,84 +1004,84 @@
         <v>11</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>8</v>
@@ -1075,7 +1090,7 @@
         <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
@@ -1089,140 +1104,186 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>83</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1234,24 +1295,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="70" customWidth="1"/>
+    <col min="4" max="4" width="75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -1259,72 +1320,58 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1336,10 +1383,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="110" style="4" customWidth="1"/>
+    <col min="1" max="1" width="115" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1349,57 +1396,67 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MACROPAGE-Quiz-API-Endpoints.xlsx
+++ b/docs/MACROPAGE-Quiz-API-Endpoints.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="124">
   <si>
     <t>Group</t>
   </si>
@@ -132,7 +132,7 @@
     <t>SanitizedQuestion[]: [{ id, text, order, timeLimitSeconds, type: "mindset"|"trivia", dimension?, options: [{key, text}] }]</t>
   </si>
   <si>
-    <t>THIS PARTICIPANT'S OWN question set, not a shared session list: 5 mindset questions (one randomly sampled per dimension from the bank, assigned on first call and persisted on Participant.assignedQuestionIds — same set returned on every later call/reload) + the session's shared trivia questions appended after. 400 if session is still "draft". No correct-answer/points info exposed.</t>
+    <t>THIS PARTICIPANT'S OWN question set, not a shared session list: 5 mindset questions (one randomly sampled per dimension from the bank, assigned on first call and persisted on Participant.assignedQuestionIds — same set returned on every later call/reload) + the session's shared trivia questions appended after. 400 unless status is "in_progress" or "ended" (i.e. still blocked during "draft" and "registration_open"). No correct-answer/points info exposed.</t>
   </si>
   <si>
     <t>Sessions (Admin)</t>
@@ -147,7 +147,7 @@
     <t>QuizSession document (_id, status: "draft", questionIds: [] — trivia only)</t>
   </si>
   <si>
-    <t>Creates a session. Mindset questions are NOT configured here — they are assigned per participant, not per session. Optionally appends trivia: triviaQuestionIds is an explicit, ordered pick (takes priority if both are sent); triviaCount randomly samples that many from the trivia bank via $sample. Registration is open immediately — no separate open-registration step.</t>
+    <t>Creates a session. Mindset questions are NOT configured here — they are assigned per participant, not per session. Optionally appends trivia: triviaQuestionIds is an explicit, ordered pick (takes priority if both are sent); triviaCount randomly samples that many from the trivia bank via $sample. Registration is NOT open yet — admin must call open-registration below.</t>
   </si>
   <si>
     <t>QuizSession[] — every session ever created, newest first (sorted by createdAt desc)</t>
@@ -156,13 +156,22 @@
     <t>Quiz history / session picker. Sessions are never deleted, so past events (and their leaderboard/participants/export) stay browsable via this list + the existing per-session routes below.</t>
   </si>
   <si>
+    <t>/api/sessions/:id/open-registration</t>
+  </si>
+  <si>
+    <t>Updated QuizSession (status: "registration_open")</t>
+  </si>
+  <si>
+    <t>Only valid from status "draft". Once open, participants can call POST /api/participants/register — it 400s at every other status.</t>
+  </si>
+  <si>
     <t>/api/sessions/:id/start</t>
   </si>
   <si>
     <t>Updated QuizSession (status: "in_progress")</t>
   </si>
   <si>
-    <t>Only valid from status "draft". 400s if the global mindset bank is empty (call POST /api/questions/mindset/seed first) — this replaced the old "session has no questions configured" check, since mindset is no longer session-scoped.</t>
+    <t>Only valid from status "registration_open". 400s if the global mindset bank is empty (call POST /api/questions/mindset/seed first) — this replaced the old "session has no questions configured" check, since mindset is no longer session-scoped.</t>
   </si>
   <si>
     <t>/api/sessions/:id/end</t>
@@ -171,7 +180,7 @@
     <t>Updated QuizSession (status: "ended")</t>
   </si>
   <si>
-    <t>Only valid from "in_progress". Broadcasts session:state + quiz:ended + a final leaderboard:update. There is no "next question" admin control — the whole state machine is draft -&gt; in_progress -&gt; ended.</t>
+    <t>Only valid from "in_progress". Broadcasts session:state + quiz:ended + a final leaderboard:update. There is no "next question" admin control — the full state machine is draft -&gt; registration_open -&gt; in_progress -&gt; ended.</t>
   </si>
   <si>
     <t>/api/sessions/:id/leaderboard</t>
@@ -228,7 +237,7 @@
     <t>{ participantId: string, sessionToken: string }</t>
   </si>
   <si>
-    <t>Works any time the session is not yet "ended" — participants can land on the session URL directly and register whenever, no separate registration-open gate. Store sessionToken client-side (localStorage) — it is the bearer token for all subsequent participant calls.</t>
+    <t>Only accepted while session.status === "registration_open" (admin must call POST /api/sessions/:id/open-registration first) — 400 at any other status. Store sessionToken client-side (localStorage) — it is the bearer token for all subsequent participant calls.</t>
   </si>
   <si>
     <t>PATCH</t>
@@ -345,7 +354,7 @@
     <t>Socket.IO namespace: /quiz (e.g. io("https://&lt;host&gt;/quiz")).</t>
   </si>
   <si>
-    <t>State machine: draft -&gt; in_progress -&gt; ended. Only two admin actions: POST /api/sessions/:id/start and POST /api/sessions/:id/end. There is no "open registration" step and no "next question" step.</t>
+    <t>State machine: draft -&gt; registration_open -&gt; in_progress -&gt; ended, strictly linear. Three admin actions drive it: POST /api/sessions/:id/open-registration, POST /api/sessions/:id/start, POST /api/sessions/:id/end. There is no "next question" step.</t>
   </si>
   <si>
     <t>PERSONALIZED QUESTIONS: each participant gets their own random pick of 1 mindset question per dimension (5 total, from a 15-question bank with 3 variants per dimension), assigned on their first GET /api/questions/:sessionId call and persisted on Participant.assignedQuestionIds — the same set is returned on every later call. Different participants very likely see different specific wording for the same dimension. This guarantees full dimension coverage per participant, so the AI analysis always has complete data.</t>
@@ -357,7 +366,7 @@
     <t>Session history: sessions are never deleted. GET /api/sessions lists all of them (newest first) so past events stay browsable via the existing per-session leaderboard/participants/export routes.</t>
   </si>
   <si>
-    <t>Registration: participants can register any time the session is not "ended" — there is no gating status to check first.</t>
+    <t>Registration: only accepted while session.status === "registration_open" — the admin must explicitly open it via POST /api/sessions/:id/open-registration before the QR/join URL will accept POST /api/participants/register.</t>
   </si>
   <si>
     <t>No socket event carries question content. Once session:state.status becomes in_progress, the client must call GET /api/questions/:sessionId (bearer sessionToken) to fetch its own set — this was previously a broadcast "questions:all" socket event, removed because content is now personalized per participant and cannot be broadcast identically to a room.</t>
@@ -770,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1061,7 +1070,7 @@
         <v>40</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>53</v>
@@ -1070,7 +1079,7 @@
         <v>22</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>54</v>
@@ -1127,88 +1136,88 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>78</v>
@@ -1219,71 +1228,94 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>90</v>
+      <c r="F23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1306,13 +1338,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -1320,58 +1352,58 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1396,67 +1428,67 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
